--- a/outputs/analysis/channel_roi.xlsx
+++ b/outputs/analysis/channel_roi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Channel</t>
   </si>
@@ -88,7 +88,37 @@
     <t>other_marketing</t>
   </si>
   <si>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>54.3%</t>
+  </si>
+  <si>
+    <t>28.9%</t>
+  </si>
+  <si>
+    <t>12.1%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
+  </si>
+  <si>
+    <t>12.2%</t>
+  </si>
+  <si>
     <t>0.0%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>28.6%</t>
+  </si>
+  <si>
+    <t>100.0%</t>
   </si>
   <si>
     <t>59.2%</t>
@@ -502,10 +532,10 @@
         <v>14813748.66</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>2456816.16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
         <v>24</v>
@@ -514,7 +544,7 @@
         <v>13273.96833333333</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -534,19 +564,19 @@
         <v>3188158.65</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1172387.77</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>2333.93751830161</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -566,19 +596,19 @@
         <v>2806070</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1164232</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>9642.852233676977</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -598,19 +628,19 @@
         <v>1535086</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>171745</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>13233.5</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -630,19 +660,19 @@
         <v>1100230</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>294824</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G6">
         <v>9245.63025210084</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -662,19 +692,19 @@
         <v>677725</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>51505</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>15402.84090909091</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -694,19 +724,19 @@
         <v>624991</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>83721</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>15243.68292682927</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -732,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G9">
         <v>991.5923913043479</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -761,16 +791,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>989.0666666666667</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I10">
         <v>1186809.5</v>
@@ -796,19 +826,19 @@
         <v>39232</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>19232</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G11">
         <v>5604.571428571428</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -834,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G12">
         <v>30000</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I12">
         <v>34546.99</v>
@@ -866,19 +896,19 @@
         <v>15409</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>15409</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G13">
         <v>15409</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I13">
         <v>0</v>

--- a/outputs/analysis/channel_roi.xlsx
+++ b/outputs/analysis/channel_roi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>Channel</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Deals</t>
   </si>
   <si>
+    <t>Resolved Deals</t>
+  </si>
+  <si>
     <t>Total Pipeline ($)</t>
   </si>
   <si>
@@ -31,7 +34,10 @@
     <t>Won Deals</t>
   </si>
   <si>
-    <t>Win Rate</t>
+    <t>Closed-Deal Win Rate</t>
+  </si>
+  <si>
+    <t>Resolved Share</t>
   </si>
   <si>
     <t>Avg Deal Size ($)</t>
@@ -88,37 +94,67 @@
     <t>other_marketing</t>
   </si>
   <si>
-    <t>17.4%</t>
-  </si>
-  <si>
-    <t>54.3%</t>
-  </si>
-  <si>
-    <t>28.9%</t>
-  </si>
-  <si>
-    <t>12.1%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>11.4%</t>
-  </si>
-  <si>
-    <t>12.2%</t>
+    <t>22.4%</t>
+  </si>
+  <si>
+    <t>57.1%</t>
+  </si>
+  <si>
+    <t>32.6%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>23.1%</t>
+  </si>
+  <si>
+    <t>14.7%</t>
+  </si>
+  <si>
+    <t>16.7%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>28.6%</t>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>33.3%</t>
   </si>
   <si>
     <t>100.0%</t>
+  </si>
+  <si>
+    <t>77.9%</t>
+  </si>
+  <si>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>88.7%</t>
+  </si>
+  <si>
+    <t>88.8%</t>
+  </si>
+  <si>
+    <t>87.4%</t>
+  </si>
+  <si>
+    <t>77.3%</t>
+  </si>
+  <si>
+    <t>73.2%</t>
+  </si>
+  <si>
+    <t>51.1%</t>
+  </si>
+  <si>
+    <t>95.6%</t>
+  </si>
+  <si>
+    <t>85.7%</t>
   </si>
   <si>
     <t>59.2%</t>
@@ -480,10 +516,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,400 +556,478 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>1120</v>
       </c>
       <c r="C2">
+        <v>872</v>
+      </c>
+      <c r="D2">
         <v>14813748.66</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2456816.16</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>195</v>
       </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2">
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2">
         <v>13273.96833333333</v>
       </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>1366</v>
       </c>
       <c r="C3">
+        <v>1299</v>
+      </c>
+      <c r="D3">
         <v>3188158.65</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1172387.77</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>742</v>
       </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3">
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3">
         <v>2333.93751830161</v>
       </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>291</v>
       </c>
       <c r="C4">
+        <v>258</v>
+      </c>
+      <c r="D4">
         <v>2806070</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1164232</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>84</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4">
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4">
         <v>9642.852233676977</v>
       </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>116</v>
       </c>
       <c r="C5">
+        <v>103</v>
+      </c>
+      <c r="D5">
         <v>1535086</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>171745</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5">
         <v>13233.5</v>
       </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>119</v>
       </c>
       <c r="C6">
+        <v>104</v>
+      </c>
+      <c r="D6">
         <v>1100230</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>294824</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6">
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6">
         <v>9245.63025210084</v>
       </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>44</v>
       </c>
       <c r="C7">
+        <v>34</v>
+      </c>
+      <c r="D7">
         <v>677725</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>51505</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7">
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7">
         <v>15402.84090909091</v>
       </c>
-      <c r="H7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="J7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>41</v>
       </c>
       <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
         <v>624991</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>83721</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>5</v>
       </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8">
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8">
         <v>15243.68292682927</v>
       </c>
-      <c r="H8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>92</v>
       </c>
       <c r="C9">
+        <v>47</v>
+      </c>
+      <c r="D9">
         <v>91226.5</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9">
         <v>991.5923913043479</v>
       </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>90</v>
       </c>
       <c r="C10">
+        <v>86</v>
+      </c>
+      <c r="D10">
         <v>89016</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10">
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10">
         <v>989.0666666666667</v>
       </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10">
+      <c r="J10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10">
         <v>1186809.5</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.08</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>13186.77</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
         <v>39232</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>19232</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11">
         <v>5604.571428571428</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="J11" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>30000</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12">
         <v>30000</v>
       </c>
-      <c r="H12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12">
+      <c r="J12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12">
         <v>34546.99</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>0.87</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>34546.99</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13">
-        <v>15409</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>15409</v>
       </c>
       <c r="E13">
+        <v>15409</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13">
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13">
         <v>15409</v>
       </c>
-      <c r="H13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="L13">
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
     </row>
